--- a/web/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
+++ b/web/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -762,7 +762,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C号屋</t>
+          <t>D号屋</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5625</v>
+        <v>5551</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>D号屋</t>
+          <t>E号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5551</v>
+        <v>7400</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>E号屋</t>
+          <t>F号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7400</v>
+        <v>5262</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>F号屋</t>
+          <t>G号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5262</v>
+        <v>5096</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>G号屋</t>
+          <t>H号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5096</v>
+        <v>4963</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1004,56 +1004,6 @@
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>H号屋</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>4963</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1074,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1085,7 +1035,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1130,7 +1079,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>7 套</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -1155,7 +1104,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>7 套</t>
         </is>
       </c>
     </row>
@@ -1177,30 +1126,25 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>C号屋</t>
+          <t>D号屋</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>D号屋</t>
+          <t>E号屋</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>E号屋</t>
+          <t>F号屋</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>F号屋</t>
+          <t>G号屋</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G号屋</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>H号屋</t>
         </is>
@@ -1232,15 +1176,6 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>C号屋
-5625呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
           <t>D号屋
 5551呎 (4+房)
 (待售)
@@ -1248,7 +1183,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>E号屋
 7400呎 (4+房)
@@ -1257,7 +1192,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>F号屋
 5262呎 (4+房)
@@ -1266,7 +1201,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>G号屋
 5096呎 (4+房)
@@ -1275,7 +1210,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>H号屋
 4963呎 (4+房)
@@ -1287,7 +1222,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
+++ b/web/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -762,7 +762,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>D号屋</t>
+          <t>C号屋</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5551</v>
+        <v>5625</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>E号屋</t>
+          <t>D号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7400</v>
+        <v>5551</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>F号屋</t>
+          <t>E号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5262</v>
+        <v>7400</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>G号屋</t>
+          <t>F号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5096</v>
+        <v>5262</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -962,48 +962,98 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>G号屋</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>5096</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>H号屋</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>4963</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1024,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1035,6 +1085,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1079,7 +1130,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>7 套</t>
+          <t>8 套</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -1104,7 +1155,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>7 套</t>
+          <t>8 套</t>
         </is>
       </c>
     </row>
@@ -1126,25 +1177,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>C号屋</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>D号屋</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>E号屋</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>F号屋</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>G号屋</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>H号屋</t>
         </is>
@@ -1176,6 +1232,15 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
+          <t>C号屋
+5625呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
           <t>D号屋
 5551呎 (4+房)
 (待售)
@@ -1183,7 +1248,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>E号屋
 7400呎 (4+房)
@@ -1192,7 +1257,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>F号屋
 5262呎 (4+房)
@@ -1201,7 +1266,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>G号屋
 5096呎 (4+房)
@@ -1210,7 +1275,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>H号屋
 4963呎 (4+房)
@@ -1222,7 +1287,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
+++ b/web/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1009,56 +1009,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>H号屋</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>4963</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -1074,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1085,7 +1035,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1130,7 +1079,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>7 套</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -1155,7 +1104,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>7 套</t>
         </is>
       </c>
     </row>
@@ -1198,11 +1147,6 @@
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>G号屋</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H号屋</t>
         </is>
       </c>
     </row>
@@ -1275,19 +1219,10 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>H号屋
-4963呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
